--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487804_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487804_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7554</v>
+        <v>6.7532</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2611</v>
+        <v>7.1121</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5057</v>
+        <v>-0.3589</v>
       </c>
       <c r="G2" t="n">
         <v>4.332</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.306</v>
+        <v>-0.3083</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5905</v>
+        <v>-0.7396</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2845</v>
+        <v>0.4313</v>
       </c>
       <c r="V2" t="n">
         <v>2.1051</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1497</v>
+        <v>3.2568</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0899</v>
+        <v>4.197</v>
       </c>
       <c r="F3" t="n">
         <v>-0.9402</v>
@@ -688,10 +688,10 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5715</v>
+        <v>-0.4643</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U3" t="n">
         <v>0.0809</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5726</v>
+        <v>2.0729</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5583</v>
+        <v>1.7975</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9857</v>
+        <v>0.2754</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1035</v>
+        <v>4.1767</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4943</v>
+        <v>-1.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5979</v>
+        <v>5.2128</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6428</v>
+        <v>5.1444</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5225</v>
+        <v>-0.4929</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1653</v>
+        <v>5.6374</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5393</v>
+        <v>-0.9678</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9719</v>
+        <v>-0.5432</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5674</v>
+        <v>-0.4245</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5715</v>
+        <v>-0.1662</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0439</v>
+        <v>-0.7038</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4724</v>
+        <v>0.5376</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.5213</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X4" t="n">
         <v>-1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.237</v>
+        <v>1.9593</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1965</v>
+        <v>2.945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0405</v>
+        <v>-0.9857</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1767</v>
+        <v>1.1035</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0362</v>
+        <v>-1.4943</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2128</v>
+        <v>2.5979</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1444</v>
+        <v>2.6428</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4929</v>
+        <v>-0.5225</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6374</v>
+        <v>3.1653</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9678</v>
+        <v>-1.5393</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5432</v>
+        <v>-0.9719</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4245</v>
+        <v>-0.5674</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0021</v>
+        <v>-0.1848</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3049</v>
+        <v>-0.6572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3028</v>
+        <v>0.4724</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5213</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
         <v>-1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2664</v>
+        <v>-0.3025</v>
       </c>
       <c r="E6" t="n">
-        <v>0.538</v>
+        <v>0.1746</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2716</v>
+        <v>-0.4771</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5659999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9812</v>
+        <v>0.4123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0066</v>
+        <v>-0.37</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9878</v>
+        <v>0.7823</v>
       </c>
       <c r="V6" t="n">
         <v>-1.3975</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4359</v>
+        <v>-0.5468</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3592</v>
+        <v>-0.2939</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0767</v>
+        <v>-0.2528</v>
       </c>
       <c r="G7" t="n">
         <v>1.4424</v>
@@ -1000,13 +1000,13 @@
         <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0646</v>
+        <v>-0.1755</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.721</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6564</v>
+        <v>0.4802</v>
       </c>
       <c r="V7" t="n">
         <v>-1.3975</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9056</v>
+        <v>-1.023</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0658</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8398</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.7502</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2583</v>
+        <v>-0.3758</v>
       </c>
       <c r="T8" t="n">
         <v>-0.261</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0026</v>
+        <v>-0.1148</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3975</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6239</v>
+        <v>-1.1263</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7356</v>
+        <v>-1.4141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1117</v>
+        <v>0.2878</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4709</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5474</v>
+        <v>-0.0498</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5219</v>
+        <v>-0.2005</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0254</v>
+        <v>0.1507</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8794</v>
+        <v>-4.581</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.414</v>
+        <v>-5.0569</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5346</v>
+        <v>0.4759</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4953</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2996</v>
+        <v>0.5979</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5806</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.719</v>
+        <v>0.6603</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9376</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.1363</v>
+        <v>6.462600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9.069199999999999</v>
+        <v>9.395500000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9329</v>
+        <v>-2.9328</v>
       </c>
       <c r="G11" t="n">
         <v>12.307</v>
@@ -1312,13 +1312,13 @@
         <v>11.4466</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0406</v>
+        <v>-0.7145</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.521599999999999</v>
+        <v>-4.195500000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>3.481</v>
+        <v>3.4809</v>
       </c>
       <c r="V11" t="n">
         <v>-5.130099999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7664</v>
+        <v>4.1158</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8214</v>
+        <v>4.4643</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.055</v>
+        <v>-0.3486</v>
       </c>
       <c r="G12" t="n">
         <v>0.2144</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2701</v>
+        <v>0.0793</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5658</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2958</v>
+        <v>1.0022</v>
       </c>
       <c r="V12" t="n">
         <v>2.9896</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3818</v>
+        <v>1.7585</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0517</v>
+        <v>2.818</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3301</v>
+        <v>-1.0595</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7958</v>
+        <v>2.4602</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7526</v>
+        <v>1.9165</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9568</v>
+        <v>0.5437</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.06560000000000001</v>
+        <v>3.1256</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6096</v>
+        <v>1.8716</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6752</v>
+        <v>1.254</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8613</v>
+        <v>-0.6654</v>
       </c>
       <c r="N13" t="n">
-        <v>1.143</v>
+        <v>0.0449</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2817</v>
+        <v>-0.7103</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4373</v>
+        <v>-0.1367</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8416</v>
+        <v>-0.3076</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5957</v>
+        <v>0.171</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3975</v>
+        <v>-1.3975</v>
       </c>
       <c r="W13" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3093</v>
+        <v>1.5255</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6037</v>
+        <v>0.33</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2944</v>
+        <v>1.1956</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4602</v>
+        <v>3.2159</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9165</v>
+        <v>4.6332</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5437</v>
+        <v>-1.4173</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1256</v>
+        <v>1.832</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8716</v>
+        <v>3.3963</v>
       </c>
       <c r="L14" t="n">
-        <v>1.254</v>
+        <v>-1.5643</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6654</v>
+        <v>1.3838</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0449</v>
+        <v>1.2369</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7103</v>
+        <v>0.147</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5859</v>
+        <v>0.1577</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5219</v>
+        <v>-0.4615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0639</v>
+        <v>0.6192</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.3975</v>
+        <v>-2.2643</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3975</v>
+        <v>-2.2643</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.116</v>
+        <v>1.4952</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1945</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1075</v>
+        <v>1.3007</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2159</v>
+        <v>0.7958</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6332</v>
+        <v>1.7526</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4173</v>
+        <v>-0.9568</v>
       </c>
       <c r="J15" t="n">
-        <v>1.832</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3963</v>
+        <v>0.6096</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5643</v>
+        <v>-0.6752</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3838</v>
+        <v>0.8613</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2369</v>
+        <v>1.143</v>
       </c>
       <c r="O15" t="n">
-        <v>0.147</v>
+        <v>-0.2817</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2518</v>
+        <v>0.5506</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>-0.0157</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5311</v>
+        <v>0.5663</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2643</v>
+        <v>1.3975</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.2643</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>G. VILLAREJO COSTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5692</v>
+        <v>0.663</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4345</v>
+        <v>1.0308</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1347</v>
+        <v>-0.3678</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0049</v>
+        <v>0.2483</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8294</v>
+        <v>0.8891</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1755</v>
+        <v>-0.6409</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0407</v>
+        <v>1.228</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6656</v>
+        <v>1.228</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7063</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0456</v>
+        <v>-0.9798</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1637</v>
+        <v>-0.3389</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8818</v>
+        <v>-0.6409</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6708</v>
+        <v>-0.0233</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6425</v>
+        <v>-0.2191</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0283</v>
+        <v>0.1957</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0708</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.0708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VILLAREJO COSTA</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4384</v>
+        <v>-0.4649</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9237</v>
+        <v>-0.2316</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4853</v>
+        <v>-0.2334</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2483</v>
+        <v>-4.1643</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8891</v>
+        <v>-2.8637</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6409</v>
+        <v>-1.3005</v>
       </c>
       <c r="J17" t="n">
-        <v>1.228</v>
+        <v>-1.7841</v>
       </c>
       <c r="K17" t="n">
-        <v>1.228</v>
+        <v>-1.9409</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1568</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9798</v>
+        <v>-2.3801</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3389</v>
+        <v>-0.9228</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6409</v>
+        <v>-1.4573</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.2081</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2479</v>
+        <v>-0.0613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3262</v>
+        <v>-0.6805</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.6192</v>
       </c>
       <c r="V17" t="n">
-        <v>0.23</v>
+        <v>2.5119</v>
       </c>
       <c r="W17" t="n">
-        <v>0.23</v>
+        <v>2.4412</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6293</v>
+        <v>-0.6008</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6602</v>
+        <v>-0.5299</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0309</v>
+        <v>-0.0709</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.1643</v>
+        <v>-2.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8637</v>
+        <v>-1.8294</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3005</v>
+        <v>-0.1755</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7841</v>
+        <v>1.0407</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9409</v>
+        <v>-0.6656</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1568</v>
+        <v>1.7063</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3801</v>
+        <v>-3.0456</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9228</v>
+        <v>-1.1637</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4573</v>
+        <v>-1.8818</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2257</v>
+        <v>0.5009</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1091</v>
+        <v>-0.3219</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8834</v>
+        <v>0.8228</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5119</v>
+        <v>0.0708</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4412</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0.0708</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2625</v>
+        <v>-1.195</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2454</v>
+        <v>-0.0311</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0171</v>
+        <v>-1.1639</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7642</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2936</v>
+        <v>0.3611</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5546</v>
+        <v>0.4078</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7678</v>
+        <v>-5.5035</v>
       </c>
       <c r="E20" t="n">
         <v>-2.1469</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6209</v>
+        <v>-3.3566</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4515</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4515</v>
+        <v>-0.1873</v>
       </c>
       <c r="T20" t="n">
         <v>-0.199</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2525</v>
+        <v>0.0118</v>
       </c>
       <c r="V20" t="n">
         <v>1.0083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.0579</v>
+        <v>-7.9302</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8581</v>
+        <v>-2.9653</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.1998</v>
+        <v>-4.9649</v>
       </c>
       <c r="G21" t="n">
         <v>-6.8566</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3282</v>
+        <v>-0.2005</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.199</v>
+        <v>-0.3062</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1292</v>
+        <v>0.1057</v>
       </c>
       <c r="V21" t="n">
         <v>0.5838</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.136400000000001</v>
+        <v>-6.1364</v>
       </c>
       <c r="E22" t="n">
-        <v>2.932900000000001</v>
+        <v>2.932799999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.069299999999998</v>
+        <v>-9.0693</v>
       </c>
       <c r="G22" t="n">
         <v>-12.3069</v>
@@ -2146,7 +2146,7 @@
         <v>7.370299999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>4.900599999999999</v>
+        <v>4.900600000000001</v>
       </c>
       <c r="L22" t="n">
         <v>2.4696</v>
@@ -2170,16 +2170,16 @@
         <v>11.4465</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0406</v>
+        <v>1.0405</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.4808</v>
+        <v>-3.4811</v>
       </c>
       <c r="U22" t="n">
-        <v>4.521599999999999</v>
+        <v>4.521699999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>5.130100000000001</v>
+        <v>5.1301</v>
       </c>
       <c r="W22" t="n">
         <v>10.49</v>
